--- a/库存物料清单.xlsx
+++ b/库存物料清单.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PCB_pro\Material\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D9432A-4EC4-426F-B5CE-4A96AF8C7E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F152CA-7CF5-4920-82FC-062EDE315D4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="元件盘" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="149">
   <si>
     <t>A</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -177,11 +177,6 @@
   <si>
     <t>0603电阻
 0Ω</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SOT-23三极管
-NPN</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -223,11 +218,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1206电容
-10uF/10V</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SOT23-6 ESD静电保护二极管
 UL26</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -282,10 +272,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>L7805</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>P6KE 6.8CA</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -303,10 +289,6 @@
   </si>
   <si>
     <t>晶振8M</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>78M05</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -524,18 +506,6 @@
   </si>
   <si>
     <t>USB母头(针式)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5mm静音按键</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10mm按键</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>纽扣电池+座</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -582,18 +552,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1位拨码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、2位带小数点数码管</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2.54mm/4P卧式接线座</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2.54mm/4P/8P插针接线座90°</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -602,10 +564,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>4.7uF电解电容</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>DC电源公头/母头</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -627,10 +585,6 @@
   </si>
   <si>
     <t>USB外壳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10K插线电阻</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -678,7 +632,92 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2.54mm 2x10弯针双排带扣/带鼻</t>
+    <t>SOT-23三极管
+NPN(8050)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0603电容
+2.2uF/16V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1206电容
+10uF/50V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10K直插电阻
+3mm直插LED
+5mm直插LED</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.54mm/4P卧式接线座
+2mm/4P卧式接线座
+FPC座8P/1.0mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1位拨码
+蜂鸣器12V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>双通铜柱/M3*22
+MOS管/SI2300/丝印2300/SOT-23
+MOS管/SI2301/丝印A1SHB/SOT-23
+MOS管/SI2302/丝印A2SHB/SOT-23
+MOS管/SI2303/丝印A3SHB/SOT-23
+MOS管/SI2306/丝印A6SHB/SOT-23
+MOS管/SI2308/丝印A8SHB/SOT-23
+MOS管/AO3400/丝印A09T/SOT-23
+MOS管/AO3401/丝印A19T/SOT-23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H10mm按键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H5mm静音按键(贴片)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>78M05贴片</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>L7805贴片</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DB207S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>开关电源变压器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.7uF/25V电解电容
+470uF/35V电解电容
+22uF/450V电解电容
+470uF/50V电解电容
+10uF/50V电解电容</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>塑封保险丝5A/250V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>纽扣电池+座
+PTC热敏电阻390M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OB2500PCP电源芯片</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -797,7 +836,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -822,7 +861,7 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
@@ -830,48 +869,85 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="thin">
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom/>
@@ -879,26 +955,17 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="thin">
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right/>
@@ -907,32 +974,49 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right/>
       <top/>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -941,7 +1025,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -987,6 +1071,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -999,8 +1086,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1011,24 +1101,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1038,34 +1122,46 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1370,7 +1466,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A2" s="19">
+      <c r="A2" s="20">
         <v>1</v>
       </c>
       <c r="B2" s="4"/>
@@ -1401,7 +1497,7 @@
       <c r="K2" s="2"/>
     </row>
     <row r="3" spans="1:11" ht="33" x14ac:dyDescent="0.45">
-      <c r="A3" s="19"/>
+      <c r="A3" s="20"/>
       <c r="B3" s="8">
         <v>1</v>
       </c>
@@ -1431,7 +1527,7 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="33" x14ac:dyDescent="0.45">
-      <c r="A4" s="19"/>
+      <c r="A4" s="20"/>
       <c r="B4" s="8">
         <v>2</v>
       </c>
@@ -1461,7 +1557,7 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="33" x14ac:dyDescent="0.45">
-      <c r="A5" s="19"/>
+      <c r="A5" s="20"/>
       <c r="B5" s="8">
         <v>3</v>
       </c>
@@ -1491,7 +1587,7 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A8" s="20">
+      <c r="A8" s="21">
         <v>2</v>
       </c>
       <c r="B8" s="9"/>
@@ -1521,95 +1617,97 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="49.5" x14ac:dyDescent="0.45">
-      <c r="A9" s="20"/>
+      <c r="A9" s="21"/>
       <c r="B9" s="12">
         <v>1</v>
       </c>
       <c r="C9" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="G9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="H9" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="J9" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>37</v>
-      </c>
     </row>
     <row r="10" spans="1:11" ht="33" x14ac:dyDescent="0.45">
-      <c r="A10" s="20"/>
+      <c r="A10" s="21"/>
       <c r="B10" s="12">
         <v>2</v>
       </c>
       <c r="C10" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="E10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="F10" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="H10" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I10" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="J10" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="H10" s="5"/>
-      <c r="I10" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="11" spans="1:11" ht="33" x14ac:dyDescent="0.45">
-      <c r="A11" s="20"/>
+      <c r="A11" s="21"/>
       <c r="B11" s="12">
         <v>3</v>
       </c>
       <c r="C11" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="F11" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="H11" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="H11" s="6" t="s">
+      <c r="I11" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="I11" s="6" t="s">
-        <v>51</v>
-      </c>
       <c r="J11" s="6" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A14" s="21">
+      <c r="A14" s="22">
         <v>3</v>
       </c>
       <c r="B14" s="13"/>
@@ -1638,92 +1736,98 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A15" s="21"/>
+    <row r="15" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="22"/>
       <c r="B15" s="13">
         <v>1</v>
       </c>
       <c r="C15" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="I15" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5" t="s">
+      <c r="J15" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>56</v>
-      </c>
     </row>
     <row r="16" spans="1:11" ht="33" x14ac:dyDescent="0.45">
-      <c r="A16" s="21"/>
+      <c r="A16" s="22"/>
       <c r="B16" s="13">
         <v>2</v>
       </c>
       <c r="C16" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="H16" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="I16" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="J16" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="J16" s="11" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="17" spans="1:10" ht="33" x14ac:dyDescent="0.45">
-      <c r="A17" s="21"/>
+      <c r="A17" s="22"/>
       <c r="B17" s="13">
         <v>3</v>
       </c>
       <c r="C17" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H17" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5" t="s">
+      <c r="I17" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="J17" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="G17" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>71</v>
-      </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A20" s="20">
+      <c r="A20" s="21">
         <v>4</v>
       </c>
       <c r="B20" s="9"/>
@@ -1753,95 +1857,95 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="33" x14ac:dyDescent="0.45">
-      <c r="A21" s="20"/>
+      <c r="A21" s="21"/>
       <c r="B21" s="12">
         <v>1</v>
       </c>
       <c r="C21" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="H21" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="I21" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="J21" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>79</v>
-      </c>
     </row>
     <row r="22" spans="1:10" ht="33" x14ac:dyDescent="0.45">
-      <c r="A22" s="20"/>
+      <c r="A22" s="21"/>
       <c r="B22" s="12">
         <v>2</v>
       </c>
       <c r="C22" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="H22" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="I22" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>86</v>
-      </c>
       <c r="J22" s="3"/>
     </row>
     <row r="23" spans="1:10" ht="33" x14ac:dyDescent="0.45">
-      <c r="A23" s="20"/>
+      <c r="A23" s="21"/>
       <c r="B23" s="12">
         <v>3</v>
       </c>
       <c r="C23" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="G23" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="H23" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="I23" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="J23" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="G23" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>94</v>
-      </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A26" s="22">
+      <c r="A26" s="23">
         <v>5</v>
       </c>
       <c r="B26" s="14"/>
@@ -1871,63 +1975,63 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="33" x14ac:dyDescent="0.45">
-      <c r="A27" s="22"/>
+      <c r="A27" s="23"/>
       <c r="B27" s="16">
         <v>1</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="33" x14ac:dyDescent="0.45">
-      <c r="A28" s="22"/>
+      <c r="A28" s="23"/>
       <c r="B28" s="16">
         <v>2</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="I28" s="6"/>
       <c r="J28" s="5" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A29" s="22"/>
+      <c r="A29" s="23"/>
       <c r="B29" s="16">
         <v>3</v>
       </c>
@@ -1938,7 +2042,7 @@
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
       <c r="I29" s="6" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="J29" s="5"/>
     </row>
@@ -1957,7 +2061,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7545ECD-58B3-46F8-96EB-A878E49C3D84}">
-  <dimension ref="A2:M36"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.6640625" style="1"/>
@@ -1974,523 +2078,508 @@
     <col min="14" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A2" s="23">
+      <c r="A2" s="29">
         <v>1</v>
       </c>
-      <c r="B2" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="27" t="s">
+      <c r="B2" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" s="33"/>
+      <c r="D2" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="E2" s="33"/>
+      <c r="F2" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="G2" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="I2" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="J2" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="K2" s="39" t="s">
         <v>111</v>
       </c>
-      <c r="E2" s="29"/>
-      <c r="F2" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="G2" s="24" t="s">
-        <v>130</v>
-      </c>
-      <c r="I2" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="J2" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="K2" s="45" t="s">
-        <v>118</v>
-      </c>
-      <c r="L2" s="45" t="s">
-        <v>116</v>
-      </c>
-      <c r="M2" s="24" t="s">
-        <v>117</v>
+      <c r="L2" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="M2" s="36" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A3" s="23"/>
-      <c r="B3" s="30"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A4" s="23"/>
-      <c r="B4" s="33"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
+      <c r="A3" s="30"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="37"/>
+      <c r="M3" s="37"/>
+    </row>
+    <row r="4" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="30"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="I4" s="37"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="37"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A5" s="23"/>
-      <c r="B5" s="27" t="s">
-        <v>107</v>
+      <c r="A5" s="30"/>
+      <c r="B5" s="32" t="s">
+        <v>103</v>
       </c>
       <c r="C5" s="28"/>
       <c r="D5" s="28"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="25"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="37"/>
+      <c r="L5" s="37"/>
+      <c r="M5" s="37"/>
     </row>
     <row r="6" spans="1:13" ht="27.5" x14ac:dyDescent="0.45">
-      <c r="A6" s="23"/>
-      <c r="B6" s="30"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
+      <c r="A6" s="30"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
       <c r="H6" s="17">
         <v>1</v>
       </c>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="25"/>
-      <c r="M6" s="25"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="37"/>
+      <c r="K6" s="37"/>
+      <c r="L6" s="37"/>
+      <c r="M6" s="37"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A7" s="23"/>
-      <c r="B7" s="30"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="I7" s="25"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="25"/>
-      <c r="M7" s="25"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A8" s="23"/>
-      <c r="B8" s="33"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="I8" s="25"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="25"/>
+      <c r="A7" s="30"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="37"/>
+      <c r="L7" s="37"/>
+      <c r="M7" s="37"/>
+    </row>
+    <row r="8" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A8" s="30"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="I8" s="37"/>
+      <c r="J8" s="37"/>
+      <c r="K8" s="37"/>
+      <c r="L8" s="37"/>
+      <c r="M8" s="37"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A9" s="23"/>
-      <c r="B9" s="27" t="s">
-        <v>124</v>
+      <c r="A9" s="30"/>
+      <c r="B9" s="32" t="s">
+        <v>115</v>
       </c>
       <c r="C9" s="28"/>
       <c r="D9" s="28"/>
       <c r="E9" s="28"/>
       <c r="F9" s="28"/>
-      <c r="G9" s="29"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25"/>
-      <c r="M9" s="25"/>
+      <c r="G9" s="33"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="37"/>
+      <c r="L9" s="37"/>
+      <c r="M9" s="37"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A10" s="23"/>
-      <c r="B10" s="30"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="32"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="25"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A11" s="23"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="35"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="26"/>
-      <c r="L11" s="26"/>
-      <c r="M11" s="26"/>
-    </row>
+      <c r="A10" s="30"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="25"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="37"/>
+      <c r="K10" s="37"/>
+      <c r="L10" s="37"/>
+      <c r="M10" s="37"/>
+    </row>
+    <row r="11" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A11" s="31"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="27"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="L11" s="38"/>
+      <c r="M11" s="38"/>
+    </row>
+    <row r="14" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="15" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A15" s="23">
+      <c r="A15" s="29">
         <v>2</v>
       </c>
-      <c r="B15" s="27" t="s">
-        <v>121</v>
-      </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="G15" s="24" t="s">
-        <v>139</v>
-      </c>
-      <c r="I15" s="24" t="s">
-        <v>112</v>
-      </c>
-      <c r="J15" s="24" t="s">
+      <c r="B15" s="49" t="s">
+        <v>137</v>
+      </c>
+      <c r="C15" s="33"/>
+      <c r="D15" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="K15" s="24" t="s">
+      <c r="E15" s="33"/>
+      <c r="F15" s="39" t="s">
+        <v>135</v>
+      </c>
+      <c r="G15" s="36" t="s">
+        <v>128</v>
+      </c>
+      <c r="I15" s="36" t="s">
         <v>105</v>
       </c>
-      <c r="L15" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="M15" s="24" t="s">
+      <c r="J15" s="36" t="s">
         <v>106</v>
       </c>
+      <c r="K15" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="L15" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="M15" s="36" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A16" s="23"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="25"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="25"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A17" s="23"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="25"/>
-      <c r="L17" s="25"/>
-      <c r="M17" s="25"/>
+      <c r="A16" s="30"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="37"/>
+      <c r="G16" s="37"/>
+      <c r="I16" s="37"/>
+      <c r="J16" s="37"/>
+      <c r="K16" s="37"/>
+      <c r="L16" s="37"/>
+      <c r="M16" s="37"/>
+    </row>
+    <row r="17" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A17" s="30"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="37"/>
+      <c r="G17" s="37"/>
+      <c r="I17" s="37"/>
+      <c r="J17" s="37"/>
+      <c r="K17" s="37"/>
+      <c r="L17" s="37"/>
+      <c r="M17" s="37"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A18" s="23"/>
-      <c r="B18" s="27"/>
+      <c r="A18" s="30"/>
+      <c r="B18" s="32"/>
       <c r="C18" s="28"/>
       <c r="D18" s="28"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="I18" s="25"/>
-      <c r="J18" s="25"/>
-      <c r="K18" s="25"/>
-      <c r="L18" s="25"/>
-      <c r="M18" s="25"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="37"/>
+      <c r="I18" s="37"/>
+      <c r="J18" s="37"/>
+      <c r="K18" s="37"/>
+      <c r="L18" s="37"/>
+      <c r="M18" s="37"/>
     </row>
     <row r="19" spans="1:13" ht="27.5" x14ac:dyDescent="0.45">
-      <c r="A19" s="23"/>
-      <c r="B19" s="30"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
+      <c r="A19" s="30"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="37"/>
       <c r="H19" s="17">
         <v>2</v>
       </c>
-      <c r="I19" s="25"/>
-      <c r="J19" s="25"/>
-      <c r="K19" s="25"/>
-      <c r="L19" s="25"/>
-      <c r="M19" s="25"/>
+      <c r="I19" s="37"/>
+      <c r="J19" s="37"/>
+      <c r="K19" s="37"/>
+      <c r="L19" s="37"/>
+      <c r="M19" s="37"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A20" s="23"/>
-      <c r="B20" s="30"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="I20" s="25"/>
-      <c r="J20" s="25"/>
-      <c r="K20" s="25"/>
-      <c r="L20" s="25"/>
-      <c r="M20" s="25"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A21" s="23"/>
-      <c r="B21" s="33"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="I21" s="25"/>
-      <c r="J21" s="25"/>
-      <c r="K21" s="25"/>
-      <c r="L21" s="25"/>
-      <c r="M21" s="25"/>
+      <c r="A20" s="30"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="37"/>
+      <c r="I20" s="37"/>
+      <c r="J20" s="37"/>
+      <c r="K20" s="37"/>
+      <c r="L20" s="37"/>
+      <c r="M20" s="37"/>
+    </row>
+    <row r="21" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A21" s="30"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="I21" s="37"/>
+      <c r="J21" s="37"/>
+      <c r="K21" s="37"/>
+      <c r="L21" s="37"/>
+      <c r="M21" s="37"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A22" s="23"/>
-      <c r="B22" s="36"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="38"/>
-      <c r="I22" s="25"/>
-      <c r="J22" s="25"/>
-      <c r="K22" s="25"/>
-      <c r="L22" s="25"/>
-      <c r="M22" s="25"/>
+      <c r="A22" s="30"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="43"/>
+      <c r="I22" s="37"/>
+      <c r="J22" s="37"/>
+      <c r="K22" s="37"/>
+      <c r="L22" s="37"/>
+      <c r="M22" s="37"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A23" s="23"/>
-      <c r="B23" s="39"/>
+      <c r="A23" s="30"/>
+      <c r="B23" s="44"/>
       <c r="C23" s="40"/>
       <c r="D23" s="40"/>
       <c r="E23" s="40"/>
       <c r="F23" s="40"/>
-      <c r="G23" s="41"/>
-      <c r="I23" s="25"/>
-      <c r="J23" s="25"/>
-      <c r="K23" s="25"/>
-      <c r="L23" s="25"/>
-      <c r="M23" s="25"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A24" s="23"/>
-      <c r="B24" s="42"/>
-      <c r="C24" s="43"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="44"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="26"/>
-      <c r="K24" s="26"/>
-      <c r="L24" s="26"/>
-      <c r="M24" s="26"/>
-    </row>
+      <c r="G23" s="45"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="37"/>
+      <c r="L23" s="37"/>
+      <c r="M23" s="37"/>
+    </row>
+    <row r="24" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A24" s="31"/>
+      <c r="B24" s="46"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="48"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="38"/>
+      <c r="L24" s="38"/>
+      <c r="M24" s="38"/>
+    </row>
+    <row r="26" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="27" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A27" s="23">
+      <c r="A27" s="29">
         <v>3</v>
       </c>
-      <c r="B27" s="27" t="s">
-        <v>110</v>
-      </c>
-      <c r="C27" s="29"/>
-      <c r="D27" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="E27" s="29"/>
-      <c r="F27" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="G27" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="I27" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="J27" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="K27" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="L27" s="24" t="s">
-        <v>132</v>
-      </c>
-      <c r="M27" s="24" t="s">
-        <v>126</v>
+      <c r="B27" s="49" t="s">
+        <v>147</v>
+      </c>
+      <c r="C27" s="33"/>
+      <c r="D27" s="32" t="s">
+        <v>139</v>
+      </c>
+      <c r="E27" s="33"/>
+      <c r="F27" s="39" t="s">
+        <v>136</v>
+      </c>
+      <c r="G27" s="36" t="s">
+        <v>140</v>
+      </c>
+      <c r="I27" s="36" t="s">
+        <v>116</v>
+      </c>
+      <c r="J27" s="36" t="s">
+        <v>117</v>
+      </c>
+      <c r="K27" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="L27" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="M27" s="39" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A28" s="23"/>
-      <c r="B28" s="30"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-      <c r="I28" s="25"/>
-      <c r="J28" s="25"/>
-      <c r="K28" s="25"/>
-      <c r="L28" s="25"/>
-      <c r="M28" s="25"/>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A29" s="23"/>
-      <c r="B29" s="33"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-      <c r="I29" s="25"/>
-      <c r="J29" s="25"/>
-      <c r="K29" s="25"/>
-      <c r="L29" s="25"/>
-      <c r="M29" s="25"/>
+      <c r="A28" s="30"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="37"/>
+      <c r="I28" s="37"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="37"/>
+      <c r="M28" s="37"/>
+    </row>
+    <row r="29" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A29" s="30"/>
+      <c r="B29" s="35"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="37"/>
+      <c r="I29" s="37"/>
+      <c r="J29" s="37"/>
+      <c r="K29" s="37"/>
+      <c r="L29" s="37"/>
+      <c r="M29" s="37"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A30" s="23"/>
-      <c r="B30" s="27"/>
+      <c r="A30" s="30"/>
+      <c r="B30" s="49" t="s">
+        <v>138</v>
+      </c>
       <c r="C30" s="28"/>
       <c r="D30" s="28"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
-      <c r="I30" s="25"/>
-      <c r="J30" s="25"/>
-      <c r="K30" s="25"/>
-      <c r="L30" s="25"/>
-      <c r="M30" s="25"/>
-    </row>
-    <row r="31" spans="1:13" ht="27.5" x14ac:dyDescent="0.45">
-      <c r="A31" s="23"/>
-      <c r="B31" s="30"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="37"/>
+      <c r="I30" s="37"/>
+      <c r="J30" s="37"/>
+      <c r="K30" s="37"/>
+      <c r="L30" s="37"/>
+      <c r="M30" s="37"/>
+    </row>
+    <row r="31" spans="1:13" ht="37.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="30"/>
+      <c r="B31" s="34"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="37"/>
+      <c r="G31" s="37"/>
       <c r="H31" s="17">
         <v>3</v>
       </c>
-      <c r="I31" s="25"/>
-      <c r="J31" s="25"/>
-      <c r="K31" s="25"/>
-      <c r="L31" s="25"/>
-      <c r="M31" s="25"/>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A32" s="23"/>
-      <c r="B32" s="30"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
-      <c r="I32" s="25"/>
-      <c r="J32" s="25"/>
-      <c r="K32" s="25"/>
-      <c r="L32" s="25"/>
-      <c r="M32" s="25"/>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A33" s="23"/>
-      <c r="B33" s="33"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="34"/>
-      <c r="E33" s="35"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="I33" s="25"/>
-      <c r="J33" s="25"/>
-      <c r="K33" s="25"/>
-      <c r="L33" s="25"/>
-      <c r="M33" s="25"/>
+      <c r="I31" s="37"/>
+      <c r="J31" s="37"/>
+      <c r="K31" s="37"/>
+      <c r="L31" s="37"/>
+      <c r="M31" s="37"/>
+    </row>
+    <row r="32" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="30"/>
+      <c r="B32" s="34"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="37"/>
+      <c r="G32" s="37"/>
+      <c r="I32" s="37"/>
+      <c r="J32" s="37"/>
+      <c r="K32" s="37"/>
+      <c r="L32" s="37"/>
+      <c r="M32" s="37"/>
+    </row>
+    <row r="33" spans="1:13" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A33" s="30"/>
+      <c r="B33" s="34"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="38"/>
+      <c r="I33" s="37"/>
+      <c r="J33" s="37"/>
+      <c r="K33" s="37"/>
+      <c r="L33" s="37"/>
+      <c r="M33" s="37"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A34" s="23"/>
-      <c r="B34" s="27" t="s">
-        <v>129</v>
+      <c r="A34" s="30"/>
+      <c r="B34" s="32" t="s">
+        <v>119</v>
       </c>
       <c r="C34" s="28"/>
       <c r="D34" s="28"/>
       <c r="E34" s="28"/>
       <c r="F34" s="28"/>
-      <c r="G34" s="29"/>
-      <c r="I34" s="25"/>
-      <c r="J34" s="25"/>
-      <c r="K34" s="25"/>
-      <c r="L34" s="25"/>
-      <c r="M34" s="25"/>
+      <c r="G34" s="33"/>
+      <c r="I34" s="37"/>
+      <c r="J34" s="37"/>
+      <c r="K34" s="37"/>
+      <c r="L34" s="37"/>
+      <c r="M34" s="37"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A35" s="23"/>
-      <c r="B35" s="30"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="32"/>
-      <c r="I35" s="25"/>
-      <c r="J35" s="25"/>
-      <c r="K35" s="25"/>
-      <c r="L35" s="25"/>
-      <c r="M35" s="25"/>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A36" s="23"/>
-      <c r="B36" s="33"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="35"/>
-      <c r="I36" s="26"/>
-      <c r="J36" s="26"/>
-      <c r="K36" s="26"/>
-      <c r="L36" s="26"/>
-      <c r="M36" s="26"/>
+      <c r="A35" s="30"/>
+      <c r="B35" s="34"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="25"/>
+      <c r="I35" s="37"/>
+      <c r="J35" s="37"/>
+      <c r="K35" s="37"/>
+      <c r="L35" s="37"/>
+      <c r="M35" s="37"/>
+    </row>
+    <row r="36" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A36" s="31"/>
+      <c r="B36" s="35"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="27"/>
+      <c r="I36" s="38"/>
+      <c r="J36" s="38"/>
+      <c r="K36" s="38"/>
+      <c r="L36" s="38"/>
+      <c r="M36" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="K27:K36"/>
-    <mergeCell ref="L27:L36"/>
-    <mergeCell ref="M27:M36"/>
-    <mergeCell ref="I27:I36"/>
-    <mergeCell ref="B34:G36"/>
-    <mergeCell ref="D27:E29"/>
-    <mergeCell ref="F27:F33"/>
-    <mergeCell ref="G27:G33"/>
-    <mergeCell ref="B30:E33"/>
-    <mergeCell ref="J27:J36"/>
-    <mergeCell ref="I2:I11"/>
-    <mergeCell ref="J2:J11"/>
-    <mergeCell ref="K2:K11"/>
-    <mergeCell ref="L2:L11"/>
-    <mergeCell ref="M2:M11"/>
-    <mergeCell ref="I15:I24"/>
-    <mergeCell ref="J15:J24"/>
-    <mergeCell ref="K15:K24"/>
-    <mergeCell ref="L15:L24"/>
-    <mergeCell ref="M15:M24"/>
     <mergeCell ref="A15:A24"/>
     <mergeCell ref="A27:A36"/>
     <mergeCell ref="A2:A11"/>
@@ -2507,6 +2596,26 @@
     <mergeCell ref="B18:E21"/>
     <mergeCell ref="B22:G24"/>
     <mergeCell ref="B27:C29"/>
+    <mergeCell ref="I15:I24"/>
+    <mergeCell ref="J15:J24"/>
+    <mergeCell ref="K15:K24"/>
+    <mergeCell ref="L15:L24"/>
+    <mergeCell ref="M15:M24"/>
+    <mergeCell ref="I2:I11"/>
+    <mergeCell ref="J2:J11"/>
+    <mergeCell ref="K2:K11"/>
+    <mergeCell ref="L2:L11"/>
+    <mergeCell ref="M2:M11"/>
+    <mergeCell ref="K27:K36"/>
+    <mergeCell ref="L27:L36"/>
+    <mergeCell ref="M27:M36"/>
+    <mergeCell ref="I27:I36"/>
+    <mergeCell ref="B34:G36"/>
+    <mergeCell ref="D27:E29"/>
+    <mergeCell ref="F27:F33"/>
+    <mergeCell ref="G27:G33"/>
+    <mergeCell ref="B30:E33"/>
+    <mergeCell ref="J27:J36"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/库存物料清单.xlsx
+++ b/库存物料清单.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PCB_pro\Material\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F152CA-7CF5-4920-82FC-062EDE315D4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7486DAE3-E1C8-4BE7-903B-4B1E4B84B0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="元件盘" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="153">
   <si>
     <t>A</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -569,10 +569,6 @@
   </si>
   <si>
     <t>鳄鱼夹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>立柱、热缩套管</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -700,14 +696,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>4.7uF/25V电解电容
-470uF/35V电解电容
-22uF/450V电解电容
-470uF/50V电解电容
-10uF/50V电解电容</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>塑封保险丝5A/250V</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -718,6 +706,38 @@
   </si>
   <si>
     <t>OB2500PCP电源芯片</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.7uF/25V直插电解电容
+470uF/35V直插电解电容
+22uF/450V直插电解电容
+470uF/50V直插电解电容
+10uF/50V直插电解电容</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>22pF/50V
+0603</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1Ω/1206</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10uF/50V(4x7)
+电解电容</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>182K/1%/0805电阻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>立柱、热缩套管
+1W直插金属膜电阻1%/1K
+2W直插金属膜电阻1%/12K</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1025,13 +1045,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1074,6 +1093,84 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1085,84 +1182,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1466,585 +1485,592 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A2" s="20">
+      <c r="A2" s="45">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="7" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>7</v>
       </c>
       <c r="K2" s="2"/>
     </row>
     <row r="3" spans="1:11" ht="33" x14ac:dyDescent="0.45">
-      <c r="A3" s="20"/>
-      <c r="B3" s="8">
+      <c r="A3" s="45"/>
+      <c r="B3" s="7">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="33" x14ac:dyDescent="0.45">
-      <c r="A4" s="20"/>
-      <c r="B4" s="8">
+      <c r="A4" s="45"/>
+      <c r="B4" s="7">
         <v>2</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="33" x14ac:dyDescent="0.45">
-      <c r="A5" s="20"/>
-      <c r="B5" s="8">
+      <c r="A5" s="45"/>
+      <c r="B5" s="7">
         <v>3</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A8" s="21">
+      <c r="A8" s="46">
         <v>2</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="10" t="s">
+      <c r="B8" s="8"/>
+      <c r="C8" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="J8" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="49.5" x14ac:dyDescent="0.45">
-      <c r="A9" s="21"/>
-      <c r="B9" s="12">
+      <c r="A9" s="46"/>
+      <c r="B9" s="11">
         <v>1</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="33" x14ac:dyDescent="0.45">
+      <c r="A10" s="46"/>
+      <c r="B10" s="11">
+        <v>2</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" s="6" t="s">
+      <c r="I10" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="33" x14ac:dyDescent="0.45">
+      <c r="A11" s="46"/>
+      <c r="B11" s="11">
+        <v>3</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="J11" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="I9" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="33" x14ac:dyDescent="0.45">
-      <c r="A10" s="21"/>
-      <c r="B10" s="12">
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A14" s="47">
+        <v>3</v>
+      </c>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E14" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="33" x14ac:dyDescent="0.45">
-      <c r="A11" s="21"/>
-      <c r="B11" s="12">
+      <c r="F14" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A14" s="22">
+      <c r="G14" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="47"/>
+      <c r="B15" s="12">
+        <v>1</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="33" x14ac:dyDescent="0.45">
+      <c r="A16" s="47"/>
+      <c r="B16" s="12">
+        <v>2</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="33" x14ac:dyDescent="0.45">
+      <c r="A17" s="47"/>
+      <c r="B17" s="12">
         <v>3</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13" t="s">
+      <c r="C17" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A20" s="46">
+        <v>4</v>
+      </c>
+      <c r="B20" s="8"/>
+      <c r="C20" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D20" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E20" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F20" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G20" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="13" t="s">
+      <c r="H20" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="I14" s="13" t="s">
+      <c r="I20" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="J14" s="13" t="s">
+      <c r="J20" s="9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="22"/>
-      <c r="B15" s="13">
+    <row r="21" spans="1:10" ht="33" x14ac:dyDescent="0.45">
+      <c r="A21" s="46"/>
+      <c r="B21" s="11">
         <v>1</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="33" x14ac:dyDescent="0.45">
-      <c r="A16" s="22"/>
-      <c r="B16" s="13">
+      <c r="C21" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="33" x14ac:dyDescent="0.45">
+      <c r="A22" s="46"/>
+      <c r="B22" s="11">
         <v>2</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="J16" s="11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="33" x14ac:dyDescent="0.45">
-      <c r="A17" s="22"/>
-      <c r="B17" s="13">
+      <c r="C22" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="33" x14ac:dyDescent="0.45">
+      <c r="A23" s="46"/>
+      <c r="B23" s="11">
         <v>3</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A20" s="21">
+      <c r="C23" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A26" s="48">
+        <v>5</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="G26" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D20" s="10" t="s">
+      <c r="H26" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="I26" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="J26" s="14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="33" x14ac:dyDescent="0.45">
+      <c r="A27" s="48"/>
+      <c r="B27" s="15">
         <v>1</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="C27" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G27" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="33" x14ac:dyDescent="0.45">
+      <c r="A28" s="48"/>
+      <c r="B28" s="15">
         <v>2</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="C28" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="33" x14ac:dyDescent="0.45">
+      <c r="A29" s="48"/>
+      <c r="B29" s="15">
         <v>3</v>
       </c>
-      <c r="G20" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="J20" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="33" x14ac:dyDescent="0.45">
-      <c r="A21" s="21"/>
-      <c r="B21" s="12">
-        <v>1</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="33" x14ac:dyDescent="0.45">
-      <c r="A22" s="21"/>
-      <c r="B22" s="12">
-        <v>2</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="J22" s="3"/>
-    </row>
-    <row r="23" spans="1:10" ht="33" x14ac:dyDescent="0.45">
-      <c r="A23" s="21"/>
-      <c r="B23" s="12">
-        <v>3</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A26" s="23">
-        <v>5</v>
-      </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="G26" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="H26" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="I26" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="J26" s="15" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="33" x14ac:dyDescent="0.45">
-      <c r="A27" s="23"/>
-      <c r="B27" s="16">
-        <v>1</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="G27" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="J27" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="33" x14ac:dyDescent="0.45">
-      <c r="A28" s="23"/>
-      <c r="B28" s="16">
-        <v>2</v>
-      </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="I28" s="6"/>
-      <c r="J28" s="5" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A29" s="23"/>
-      <c r="B29" s="16">
-        <v>3</v>
-      </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6" t="s">
+      <c r="C29" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="J29" s="5"/>
+      <c r="J29" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2074,509 +2100,509 @@
     <col min="10" max="10" width="20.5" style="1" customWidth="1"/>
     <col min="11" max="11" width="20.83203125" style="1" customWidth="1"/>
     <col min="12" max="12" width="29.5" style="1" customWidth="1"/>
-    <col min="13" max="13" width="19.6640625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="23.9140625" style="1" customWidth="1"/>
     <col min="14" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A2" s="29">
+      <c r="A2" s="33">
         <v>1</v>
       </c>
-      <c r="B2" s="32" t="s">
-        <v>121</v>
-      </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="32" t="s">
+      <c r="B2" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="E2" s="33"/>
-      <c r="F2" s="36" t="s">
+      <c r="E2" s="25"/>
+      <c r="F2" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="G2" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="I2" s="36" t="s">
+      <c r="G2" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="I2" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="J2" s="36" t="s">
+      <c r="J2" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="K2" s="39" t="s">
+      <c r="K2" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="L2" s="39" t="s">
+      <c r="L2" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="M2" s="36" t="s">
+      <c r="M2" s="19" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A3" s="30"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="37"/>
-      <c r="K3" s="37"/>
-      <c r="L3" s="37"/>
-      <c r="M3" s="37"/>
+      <c r="A3" s="34"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
     </row>
     <row r="4" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="30"/>
-      <c r="B4" s="35"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="37"/>
-      <c r="K4" s="37"/>
-      <c r="L4" s="37"/>
-      <c r="M4" s="37"/>
+      <c r="A4" s="34"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A5" s="30"/>
-      <c r="B5" s="32" t="s">
+      <c r="A5" s="34"/>
+      <c r="B5" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="37"/>
-      <c r="K5" s="37"/>
-      <c r="L5" s="37"/>
-      <c r="M5" s="37"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="20"/>
     </row>
     <row r="6" spans="1:13" ht="27.5" x14ac:dyDescent="0.45">
-      <c r="A6" s="30"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="17">
+      <c r="A6" s="34"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="16">
         <v>1</v>
       </c>
-      <c r="I6" s="37"/>
-      <c r="J6" s="37"/>
-      <c r="K6" s="37"/>
-      <c r="L6" s="37"/>
-      <c r="M6" s="37"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A7" s="30"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="37"/>
-      <c r="K7" s="37"/>
-      <c r="L7" s="37"/>
-      <c r="M7" s="37"/>
+      <c r="A7" s="34"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
     </row>
     <row r="8" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="30"/>
-      <c r="B8" s="34"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="37"/>
-      <c r="L8" s="37"/>
-      <c r="M8" s="37"/>
+      <c r="A8" s="34"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A9" s="30"/>
-      <c r="B9" s="32" t="s">
+      <c r="A9" s="34"/>
+      <c r="B9" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="33"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="37"/>
-      <c r="L9" s="37"/>
-      <c r="M9" s="37"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="25"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A10" s="30"/>
-      <c r="B10" s="34"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="25"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="37"/>
-      <c r="L10" s="37"/>
-      <c r="M10" s="37"/>
+      <c r="A10" s="34"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="28"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="20"/>
     </row>
     <row r="11" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="31"/>
-      <c r="B11" s="35"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="27"/>
-      <c r="I11" s="38"/>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="L11" s="38"/>
-      <c r="M11" s="38"/>
+      <c r="A11" s="35"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="31"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="21"/>
+      <c r="L11" s="21"/>
+      <c r="M11" s="21"/>
     </row>
     <row r="14" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="15" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A15" s="29">
+      <c r="A15" s="33">
         <v>2</v>
       </c>
-      <c r="B15" s="49" t="s">
-        <v>137</v>
-      </c>
-      <c r="C15" s="33"/>
-      <c r="D15" s="32" t="s">
+      <c r="B15" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="C15" s="25"/>
+      <c r="D15" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="E15" s="33"/>
-      <c r="F15" s="39" t="s">
-        <v>135</v>
-      </c>
-      <c r="G15" s="36" t="s">
-        <v>128</v>
-      </c>
-      <c r="I15" s="36" t="s">
+      <c r="E15" s="25"/>
+      <c r="F15" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="I15" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="J15" s="36" t="s">
+      <c r="J15" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="K15" s="36" t="s">
+      <c r="K15" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="L15" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="M15" s="36" t="s">
+      <c r="L15" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="M15" s="19" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A16" s="30"/>
-      <c r="B16" s="34"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="37"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="37"/>
-      <c r="K16" s="37"/>
-      <c r="L16" s="37"/>
-      <c r="M16" s="37"/>
+      <c r="A16" s="34"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="20"/>
     </row>
     <row r="17" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A17" s="30"/>
-      <c r="B17" s="35"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="37"/>
-      <c r="I17" s="37"/>
-      <c r="J17" s="37"/>
-      <c r="K17" s="37"/>
-      <c r="L17" s="37"/>
-      <c r="M17" s="37"/>
+      <c r="A17" s="34"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A18" s="30"/>
-      <c r="B18" s="32"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37"/>
-      <c r="K18" s="37"/>
-      <c r="L18" s="37"/>
-      <c r="M18" s="37"/>
+      <c r="A18" s="34"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="20"/>
     </row>
     <row r="19" spans="1:13" ht="27.5" x14ac:dyDescent="0.45">
-      <c r="A19" s="30"/>
-      <c r="B19" s="34"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="17">
+      <c r="A19" s="34"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="16">
         <v>2</v>
       </c>
-      <c r="I19" s="37"/>
-      <c r="J19" s="37"/>
-      <c r="K19" s="37"/>
-      <c r="L19" s="37"/>
-      <c r="M19" s="37"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="20"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A20" s="30"/>
-      <c r="B20" s="34"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="37"/>
-      <c r="I20" s="37"/>
-      <c r="J20" s="37"/>
-      <c r="K20" s="37"/>
-      <c r="L20" s="37"/>
-      <c r="M20" s="37"/>
+      <c r="A20" s="34"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="20"/>
     </row>
     <row r="21" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A21" s="30"/>
-      <c r="B21" s="34"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="I21" s="37"/>
-      <c r="J21" s="37"/>
-      <c r="K21" s="37"/>
-      <c r="L21" s="37"/>
-      <c r="M21" s="37"/>
+      <c r="A21" s="34"/>
+      <c r="B21" s="26"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="20"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A22" s="30"/>
-      <c r="B22" s="41"/>
-      <c r="C22" s="42"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="43"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="37"/>
-      <c r="K22" s="37"/>
-      <c r="L22" s="37"/>
-      <c r="M22" s="37"/>
+      <c r="A22" s="34"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="38"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="20"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A23" s="30"/>
-      <c r="B23" s="44"/>
+      <c r="A23" s="34"/>
+      <c r="B23" s="39"/>
       <c r="C23" s="40"/>
       <c r="D23" s="40"/>
       <c r="E23" s="40"/>
       <c r="F23" s="40"/>
-      <c r="G23" s="45"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="37"/>
-      <c r="L23" s="37"/>
-      <c r="M23" s="37"/>
+      <c r="G23" s="41"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20"/>
     </row>
     <row r="24" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A24" s="31"/>
-      <c r="B24" s="46"/>
-      <c r="C24" s="47"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="47"/>
-      <c r="G24" s="48"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="38"/>
-      <c r="L24" s="38"/>
-      <c r="M24" s="38"/>
+      <c r="A24" s="35"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="44"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="21"/>
+      <c r="L24" s="21"/>
+      <c r="M24" s="21"/>
     </row>
     <row r="26" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="27" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A27" s="29">
+      <c r="A27" s="33">
         <v>3</v>
       </c>
-      <c r="B27" s="49" t="s">
+      <c r="B27" s="32" t="s">
+        <v>145</v>
+      </c>
+      <c r="C27" s="25"/>
+      <c r="D27" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="E27" s="25"/>
+      <c r="F27" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="I27" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="J27" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="K27" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="L27" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="M27" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="C27" s="33"/>
-      <c r="D27" s="32" t="s">
-        <v>139</v>
-      </c>
-      <c r="E27" s="33"/>
-      <c r="F27" s="39" t="s">
-        <v>136</v>
-      </c>
-      <c r="G27" s="36" t="s">
-        <v>140</v>
-      </c>
-      <c r="I27" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="J27" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="K27" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="L27" s="36" t="s">
-        <v>122</v>
-      </c>
-      <c r="M27" s="39" t="s">
-        <v>145</v>
-      </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A28" s="30"/>
-      <c r="B28" s="34"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="37"/>
-      <c r="G28" s="37"/>
-      <c r="I28" s="37"/>
-      <c r="J28" s="37"/>
-      <c r="K28" s="37"/>
-      <c r="L28" s="37"/>
-      <c r="M28" s="37"/>
+      <c r="A28" s="34"/>
+      <c r="B28" s="26"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
     </row>
     <row r="29" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A29" s="30"/>
-      <c r="B29" s="35"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="37"/>
-      <c r="G29" s="37"/>
-      <c r="I29" s="37"/>
-      <c r="J29" s="37"/>
-      <c r="K29" s="37"/>
-      <c r="L29" s="37"/>
-      <c r="M29" s="37"/>
+      <c r="A29" s="34"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="20"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A30" s="30"/>
-      <c r="B30" s="49" t="s">
-        <v>138</v>
-      </c>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="37"/>
-      <c r="G30" s="37"/>
-      <c r="I30" s="37"/>
-      <c r="J30" s="37"/>
-      <c r="K30" s="37"/>
-      <c r="L30" s="37"/>
-      <c r="M30" s="37"/>
+      <c r="A30" s="34"/>
+      <c r="B30" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="C30" s="24"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
+      <c r="M30" s="20"/>
     </row>
     <row r="31" spans="1:13" ht="37.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="30"/>
-      <c r="B31" s="34"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="37"/>
-      <c r="G31" s="37"/>
-      <c r="H31" s="17">
+      <c r="A31" s="34"/>
+      <c r="B31" s="26"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="16">
         <v>3</v>
       </c>
-      <c r="I31" s="37"/>
-      <c r="J31" s="37"/>
-      <c r="K31" s="37"/>
-      <c r="L31" s="37"/>
-      <c r="M31" s="37"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="20"/>
+      <c r="M31" s="20"/>
     </row>
     <row r="32" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="30"/>
-      <c r="B32" s="34"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="37"/>
-      <c r="G32" s="37"/>
-      <c r="I32" s="37"/>
-      <c r="J32" s="37"/>
-      <c r="K32" s="37"/>
-      <c r="L32" s="37"/>
-      <c r="M32" s="37"/>
+      <c r="A32" s="34"/>
+      <c r="B32" s="26"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="20"/>
+      <c r="L32" s="20"/>
+      <c r="M32" s="20"/>
     </row>
     <row r="33" spans="1:13" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A33" s="30"/>
-      <c r="B33" s="34"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="38"/>
-      <c r="I33" s="37"/>
-      <c r="J33" s="37"/>
-      <c r="K33" s="37"/>
-      <c r="L33" s="37"/>
-      <c r="M33" s="37"/>
+      <c r="A33" s="34"/>
+      <c r="B33" s="26"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="20"/>
+      <c r="L33" s="20"/>
+      <c r="M33" s="20"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A34" s="30"/>
+      <c r="A34" s="34"/>
       <c r="B34" s="32" t="s">
-        <v>119</v>
-      </c>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="33"/>
-      <c r="I34" s="37"/>
-      <c r="J34" s="37"/>
-      <c r="K34" s="37"/>
-      <c r="L34" s="37"/>
-      <c r="M34" s="37"/>
+        <v>152</v>
+      </c>
+      <c r="C34" s="24"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="25"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="20"/>
+      <c r="L34" s="20"/>
+      <c r="M34" s="20"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A35" s="30"/>
-      <c r="B35" s="34"/>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="25"/>
-      <c r="I35" s="37"/>
-      <c r="J35" s="37"/>
-      <c r="K35" s="37"/>
-      <c r="L35" s="37"/>
-      <c r="M35" s="37"/>
+      <c r="A35" s="34"/>
+      <c r="B35" s="26"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="28"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="20"/>
+      <c r="K35" s="20"/>
+      <c r="L35" s="20"/>
+      <c r="M35" s="20"/>
     </row>
     <row r="36" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A36" s="31"/>
-      <c r="B36" s="35"/>
-      <c r="C36" s="26"/>
-      <c r="D36" s="26"/>
-      <c r="E36" s="26"/>
-      <c r="F36" s="26"/>
-      <c r="G36" s="27"/>
-      <c r="I36" s="38"/>
-      <c r="J36" s="38"/>
-      <c r="K36" s="38"/>
-      <c r="L36" s="38"/>
-      <c r="M36" s="38"/>
+      <c r="A36" s="35"/>
+      <c r="B36" s="29"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="30"/>
+      <c r="G36" s="31"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="21"/>
+      <c r="K36" s="21"/>
+      <c r="L36" s="21"/>
+      <c r="M36" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="36">

--- a/库存物料清单.xlsx
+++ b/库存物料清单.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PCB_pro\Material\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7486DAE3-E1C8-4BE7-903B-4B1E4B84B0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2ACB08-6741-42F7-B138-463B7FB3C0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="元件盘" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="179">
   <si>
     <t>A</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -57,11 +57,6 @@
   </si>
   <si>
     <t>H</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0603x4排阻
-470Ω</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -70,36 +65,16 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0603x4排阻
-47Ω</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0603x4排阻
-33Ω</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0603电阻
 3.3KΩ</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0603电阻
-100Ω</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>5.5x5x4.5电感
 4.7uH</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0603电阻
-680Ω</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0805保险线
 5V 200mA</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -130,11 +105,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0402电阻
-0Ω</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0805磁珠
 10Ω</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -146,17 +116,7 @@
   </si>
   <si>
     <t>0603电阻
-24Ω</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0603电阻
 1KΩ 5%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0603电阻
-240Ω</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -167,16 +127,6 @@
   <si>
     <t>0603电阻
 4.7KΩ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0603电阻
-10KΩ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0603电阻
-0Ω</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -447,10 +397,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>光耦 PC817</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>485芯片
 TP8485E-SR</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -497,30 +443,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>继电器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DC3.5座</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>USB母头(针式)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>变阻器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5.08mm/2P立式接线柱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.81mm/3P立式接线柱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>TF SD卡</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -529,58 +451,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2.54mm双排插针贴片/180°
-2.54mm双排插针(长)/180°
-2mm双排插针</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2.54mm单排插针/90°</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2.54mm单排插针/180°
-2mm单排插针</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2.54mm/2P接线座</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TYPE C公座</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、2位带小数点数码管</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2.54mm/4P/8P插针接线座90°</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>B0505S隔离变压器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DC电源公头/母头</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鳄鱼夹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ai-WB2-12F WiFi&amp;BLE蓝牙二合一模组</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FPC14P/18P/40P/6P/50P座</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>USB外壳</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -599,11 +470,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0603电阻
-10Ω  1%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1206磁珠
 0Ω</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -623,11 +489,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0603电阻
-22Ω  1%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SOT-23三极管
 NPN(8050)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -643,39 +504,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10K直插电阻
-3mm直插LED
-5mm直插LED</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2.54mm/4P卧式接线座
-2mm/4P卧式接线座
-FPC座8P/1.0mm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1位拨码
-蜂鸣器12V</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>双通铜柱/M3*22
-MOS管/SI2300/丝印2300/SOT-23
-MOS管/SI2301/丝印A1SHB/SOT-23
-MOS管/SI2302/丝印A2SHB/SOT-23
-MOS管/SI2303/丝印A3SHB/SOT-23
-MOS管/SI2306/丝印A6SHB/SOT-23
-MOS管/SI2308/丝印A8SHB/SOT-23
-MOS管/AO3400/丝印A09T/SOT-23
-MOS管/AO3401/丝印A19T/SOT-23</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>H10mm按键</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>H5mm静音按键(贴片)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -692,28 +520,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>开关电源变压器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>塑封保险丝5A/250V</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>纽扣电池+座
-PTC热敏电阻390M</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>OB2500PCP电源芯片</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.7uF/25V直插电解电容
-470uF/35V直插电解电容
-22uF/450V直插电解电容
-470uF/50V直插电解电容
-10uF/50V直插电解电容</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -722,10 +533,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1Ω/1206</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>10uF/50V(4x7)
 电解电容</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -735,9 +542,318 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>立柱、热缩套管
-1W直插金属膜电阻1%/1K
-2W直插金属膜电阻1%/12K</t>
+    <t>4.7nF/100V/0805电容</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>U1SD/SMA
+整流二极管</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1SMA4736A/SMA
+贴片稳压二极管</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100pF/50V/1206
+贴片电容</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADUM3160</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拨码开关</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1SMA4745A/SMA
+贴片稳压二极管</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.8K/0805/1%
+贴片电阻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15K/0805/1%
+贴片电阻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1K/0805/1%
+贴片电阻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100K/0805/1%
+贴片电阻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0603电容
+0.1uF/50V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0603电容
+220nF/50V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100K/1206/1%
+贴片电阻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1M/1206/1%
+贴片电阻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S1M/SMA
+二极管</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2SK3018
+KN NMOS管 SOT-23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>光耦 PC817插件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.54mm双排插针贴片/180°；
+2.54mm双排插针(长)/180°；
+2mm双排插针；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.54mm/4P卧式接线座；
+2mm/4P卧式接线座；
+FPC座8P/1.0mm；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10K直插电阻；
+3mm直插LED；
+5mm直插LED；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.54mm单排插针/180°；
+2mm单排插针；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>变阻器；
+L7805/TO-220；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54mm/2P接线座；
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>USB母头(针式)；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FPC14P/18P/40P/6P/50P座；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.54mm/4P/8P插针接线座90°；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TYPE C公座；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鳄鱼夹；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC电源公头/母头；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B0505S隔离变压器；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>继电器；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>开关电源变压器；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC3.5座；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.81mm/3P立式接线柱；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5.08mm/2P立式接线柱；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、2位带小数点数码管；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ai-WB2-12F WiFi&amp;BLE蓝牙二合一模组；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0603x4排阻
+470R</t>
+  </si>
+  <si>
+    <t>0603x4排阻
+47R</t>
+  </si>
+  <si>
+    <t>0603x4排阻
+33R</t>
+  </si>
+  <si>
+    <t>0603电阻
+100R</t>
+  </si>
+  <si>
+    <t>0603电阻
+680R</t>
+  </si>
+  <si>
+    <t>0603电阻
+24R</t>
+  </si>
+  <si>
+    <t>0603电阻
+240R</t>
+  </si>
+  <si>
+    <t>0603电阻
+0R</t>
+  </si>
+  <si>
+    <t>0603电阻
+10KΩ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0603电阻
+10R  1%</t>
+  </si>
+  <si>
+    <t>0603电阻
+22R  1%</t>
+  </si>
+  <si>
+    <t>1R/1206</t>
+  </si>
+  <si>
+    <t>0402电阻
+0R</t>
+  </si>
+  <si>
+    <t>330R/0805/1%
+贴片电阻</t>
+  </si>
+  <si>
+    <t>双通铜柱/M3*22；
+MOS管/SI2300/丝印2300/SOT-23；
+MOS管/SI2301/丝印A1SHB/SOT-23；
+MOS管/SI2302/丝印A2SHB/SOT-23；
+MOS管/SI2303/丝印A3SHB/SOT-23；
+MOS管/SI2306/丝印A6SHB/SOT-23；
+MOS管/SI2308/丝印A8SHB/SOT-23；
+MOS管/AO3400/丝印A09T/SOT-23；
+MOS管/AO3401/丝印A19T/SOT-23；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>立柱、热缩套管；
+1W直插金属膜电阻1%/1K；
+2W直插金属膜电阻1%/12K；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>纽扣电池+座；
+PTC热敏电阻390M直插；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H10mm按键；
+PTC/MZ6/1K直插；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.7uF/25V直插电解电容；
+470uF/35V直插电解电容；
+22uF/450V直插电解电容；
+470uF/50V直插电解电容；
+10uF/50V直插电解电容；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>塑料柱H20mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1位拨码；
+2位拨码；
+蜂鸣器12V；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>USB外壳；
+继电器8脚1选2输出/12V；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25Q128/Flash芯片；
+SWM34SV</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.32K/0603
+贴片电阻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400Vac/472M/P7.5
+安规Y电容</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400Vac/471K/P10
+安规Y电容</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>222J/630V电容
+10mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>222K，1KV，Y5P/Y5R，D=8mm，P=5mm电容</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MZ62-202/2KΩ/PTC</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1093,6 +1209,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1106,7 +1234,7 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1132,9 +1260,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1145,6 +1270,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1170,18 +1298,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1470,7 +1586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:K29"/>
+  <dimension ref="A2:K34"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="1"/>
@@ -1485,7 +1601,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A2" s="45">
+      <c r="A2" s="20">
         <v>1</v>
       </c>
       <c r="B2" s="3"/>
@@ -1516,97 +1632,97 @@
       <c r="K2" s="2"/>
     </row>
     <row r="3" spans="1:11" ht="33" x14ac:dyDescent="0.45">
-      <c r="A3" s="45"/>
+      <c r="A3" s="20"/>
       <c r="B3" s="7">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="H3" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="J3" s="5" t="s">
-        <v>15</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="33" x14ac:dyDescent="0.45">
-      <c r="A4" s="45"/>
+      <c r="A4" s="20"/>
       <c r="B4" s="7">
         <v>2</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="I4" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>23</v>
-      </c>
     </row>
     <row r="5" spans="1:11" ht="33" x14ac:dyDescent="0.45">
-      <c r="A5" s="45"/>
+      <c r="A5" s="20"/>
       <c r="B5" s="7">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>25</v>
+        <v>155</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>27</v>
+        <v>156</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>30</v>
+        <v>158</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>31</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A8" s="46">
+      <c r="A8" s="19">
         <v>2</v>
       </c>
       <c r="B8" s="8"/>
@@ -1636,97 +1752,97 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="49.5" x14ac:dyDescent="0.45">
-      <c r="A9" s="46"/>
+      <c r="A9" s="19"/>
       <c r="B9" s="11">
         <v>1</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="33" x14ac:dyDescent="0.45">
-      <c r="A10" s="46"/>
+      <c r="A10" s="19"/>
       <c r="B10" s="11">
         <v>2</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="33" x14ac:dyDescent="0.45">
-      <c r="A11" s="46"/>
+      <c r="A11" s="19"/>
       <c r="B11" s="11">
         <v>3</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A14" s="47">
+      <c r="A14" s="21">
         <v>3</v>
       </c>
       <c r="B14" s="12"/>
@@ -1756,97 +1872,97 @@
       </c>
     </row>
     <row r="15" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="47"/>
+      <c r="A15" s="21"/>
       <c r="B15" s="12">
         <v>1</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>142</v>
+        <v>106</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="33" x14ac:dyDescent="0.45">
-      <c r="A16" s="47"/>
+      <c r="A16" s="21"/>
       <c r="B16" s="12">
         <v>2</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>140</v>
+        <v>104</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="33" x14ac:dyDescent="0.45">
-      <c r="A17" s="47"/>
+      <c r="A17" s="21"/>
       <c r="B17" s="12">
         <v>3</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A20" s="46">
+      <c r="A20" s="19">
         <v>4</v>
       </c>
       <c r="B20" s="8"/>
@@ -1876,97 +1992,97 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="33" x14ac:dyDescent="0.45">
-      <c r="A21" s="46"/>
+      <c r="A21" s="19"/>
       <c r="B21" s="11">
         <v>1</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="33" x14ac:dyDescent="0.45">
-      <c r="A22" s="46"/>
+      <c r="A22" s="19"/>
       <c r="B22" s="11">
         <v>2</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>148</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="33" x14ac:dyDescent="0.45">
-      <c r="A23" s="46"/>
+      <c r="A23" s="19"/>
       <c r="B23" s="11">
         <v>3</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>90</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A26" s="48">
+      <c r="A26" s="22">
         <v>5</v>
       </c>
       <c r="B26" s="13"/>
@@ -1996,84 +2112,208 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="33" x14ac:dyDescent="0.45">
-      <c r="A27" s="48"/>
+      <c r="A27" s="22"/>
       <c r="B27" s="15">
         <v>1</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="F27" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G27" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="H27" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="G27" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>122</v>
-      </c>
       <c r="I27" s="5" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="33" x14ac:dyDescent="0.45">
-      <c r="A28" s="48"/>
+      <c r="A28" s="22"/>
       <c r="B28" s="15">
         <v>2</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>99</v>
+        <v>88</v>
+      </c>
+      <c r="I28" s="18" t="s">
+        <v>117</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="33" x14ac:dyDescent="0.45">
-      <c r="A29" s="48"/>
+      <c r="A29" s="22"/>
       <c r="B29" s="15">
         <v>3</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
+        <v>111</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>115</v>
+      </c>
       <c r="I29" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="J29" s="4"/>
+        <v>90</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A31" s="19">
+        <v>6</v>
+      </c>
+      <c r="B31" s="8"/>
+      <c r="C31" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="33" x14ac:dyDescent="0.45">
+      <c r="A32" s="19"/>
+      <c r="B32" s="11">
+        <v>1</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="33" x14ac:dyDescent="0.45">
+      <c r="A33" s="19"/>
+      <c r="B33" s="11">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="53.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="19"/>
+      <c r="B34" s="11">
+        <v>3</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="A31:A34"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="A14:A17"/>
@@ -2096,9 +2336,9 @@
     <col min="6" max="6" width="24.6640625" style="1" customWidth="1"/>
     <col min="7" max="7" width="36.1640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="8.6640625" style="1"/>
-    <col min="9" max="9" width="19.9140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="20.5" style="1" customWidth="1"/>
-    <col min="11" max="11" width="20.83203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="26.83203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="24.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="24.08203125" style="1" customWidth="1"/>
     <col min="12" max="12" width="29.5" style="1" customWidth="1"/>
     <col min="13" max="13" width="23.9140625" style="1" customWidth="1"/>
     <col min="14" max="16384" width="8.6640625" style="1"/>
@@ -2106,503 +2346,505 @@
   <sheetData>
     <row r="1" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A2" s="33">
+      <c r="A2" s="36">
         <v>1</v>
       </c>
-      <c r="B2" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="E2" s="25"/>
-      <c r="F2" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="G2" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="I2" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="J2" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="K2" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="L2" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="M2" s="19" t="s">
-        <v>110</v>
+      <c r="B2" s="39" t="s">
+        <v>137</v>
+      </c>
+      <c r="C2" s="29"/>
+      <c r="D2" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="E2" s="29"/>
+      <c r="F2" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I2" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="J2" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="K2" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="L2" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="M2" s="23" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A3" s="34"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
+      <c r="A3" s="37"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
     </row>
     <row r="4" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="34"/>
-      <c r="B4" s="29"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
-      <c r="M4" s="20"/>
+      <c r="A4" s="37"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A5" s="34"/>
-      <c r="B5" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="20"/>
+      <c r="A5" s="37"/>
+      <c r="B5" s="39" t="s">
+        <v>136</v>
+      </c>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
     </row>
     <row r="6" spans="1:13" ht="27.5" x14ac:dyDescent="0.45">
-      <c r="A6" s="34"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
+      <c r="A6" s="37"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
       <c r="H6" s="16">
         <v>1</v>
       </c>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A7" s="34"/>
-      <c r="B7" s="26"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="20"/>
-      <c r="L7" s="20"/>
-      <c r="M7" s="20"/>
+      <c r="A7" s="37"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="24"/>
     </row>
     <row r="8" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="34"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="20"/>
-      <c r="L8" s="20"/>
-      <c r="M8" s="20"/>
+      <c r="A8" s="37"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="24"/>
+      <c r="M8" s="24"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A9" s="34"/>
-      <c r="B9" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="C9" s="24"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="25"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
+      <c r="A9" s="37"/>
+      <c r="B9" s="39" t="s">
+        <v>138</v>
+      </c>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="29"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="24"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A10" s="34"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="28"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="20"/>
-      <c r="M10" s="20"/>
+      <c r="A10" s="37"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="32"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="24"/>
     </row>
     <row r="11" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="35"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="31"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="21"/>
-      <c r="M11" s="21"/>
+      <c r="A11" s="38"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="35"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="25"/>
     </row>
     <row r="14" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="15" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A15" s="33">
+      <c r="A15" s="36">
         <v>2</v>
       </c>
-      <c r="B15" s="32" t="s">
-        <v>136</v>
-      </c>
-      <c r="C15" s="25"/>
-      <c r="D15" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" s="25"/>
-      <c r="F15" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="G15" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="I15" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="J15" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="K15" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="L15" s="19" t="s">
+      <c r="B15" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="C15" s="29"/>
+      <c r="D15" s="39" t="s">
+        <v>139</v>
+      </c>
+      <c r="E15" s="29"/>
+      <c r="F15" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="G15" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="I15" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="J15" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="K15" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="M15" s="19" t="s">
-        <v>102</v>
+      <c r="L15" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="M15" s="23" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A16" s="34"/>
-      <c r="B16" s="26"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-      <c r="M16" s="20"/>
+      <c r="A16" s="37"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="24"/>
     </row>
     <row r="17" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A17" s="34"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-      <c r="M17" s="20"/>
+      <c r="A17" s="37"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="24"/>
+      <c r="M17" s="24"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A18" s="34"/>
-      <c r="B18" s="23"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-      <c r="M18" s="20"/>
+      <c r="A18" s="37"/>
+      <c r="B18" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="24"/>
+      <c r="M18" s="24"/>
     </row>
     <row r="19" spans="1:13" ht="27.5" x14ac:dyDescent="0.45">
-      <c r="A19" s="34"/>
-      <c r="B19" s="26"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
+      <c r="A19" s="37"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
       <c r="H19" s="16">
         <v>2</v>
       </c>
-      <c r="I19" s="20"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-      <c r="M19" s="20"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="24"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="24"/>
+      <c r="M19" s="24"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A20" s="34"/>
-      <c r="B20" s="26"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-      <c r="M20" s="20"/>
+      <c r="A20" s="37"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="24"/>
+      <c r="M20" s="24"/>
     </row>
     <row r="21" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A21" s="34"/>
-      <c r="B21" s="26"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-      <c r="M21" s="20"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="24"/>
+      <c r="K21" s="24"/>
+      <c r="L21" s="24"/>
+      <c r="M21" s="24"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A22" s="34"/>
-      <c r="B22" s="36"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="38"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-      <c r="M22" s="20"/>
+      <c r="A22" s="37"/>
+      <c r="B22" s="40"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="42"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="24"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="24"/>
+      <c r="M22" s="24"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A23" s="34"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="40"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="41"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-      <c r="M23" s="20"/>
+      <c r="A23" s="37"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="45"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+      <c r="M23" s="24"/>
     </row>
     <row r="24" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A24" s="35"/>
-      <c r="B24" s="42"/>
-      <c r="C24" s="43"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="44"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="21"/>
-      <c r="K24" s="21"/>
-      <c r="L24" s="21"/>
-      <c r="M24" s="21"/>
+      <c r="A24" s="38"/>
+      <c r="B24" s="46"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="48"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
+      <c r="M24" s="25"/>
     </row>
     <row r="26" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="27" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A27" s="33">
+      <c r="A27" s="36">
         <v>3</v>
       </c>
-      <c r="B27" s="32" t="s">
-        <v>145</v>
-      </c>
-      <c r="C27" s="25"/>
-      <c r="D27" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="E27" s="25"/>
-      <c r="F27" s="22" t="s">
-        <v>135</v>
-      </c>
-      <c r="G27" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="I27" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="J27" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="K27" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="L27" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="M27" s="22" t="s">
-        <v>147</v>
+      <c r="B27" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="C27" s="29"/>
+      <c r="D27" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="E27" s="29"/>
+      <c r="F27" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="G27" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="I27" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="J27" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="K27" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="L27" s="26" t="s">
+        <v>171</v>
+      </c>
+      <c r="M27" s="26" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A28" s="34"/>
-      <c r="B28" s="26"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="20"/>
+      <c r="A28" s="37"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+      <c r="I28" s="24"/>
+      <c r="J28" s="24"/>
+      <c r="K28" s="24"/>
+      <c r="L28" s="24"/>
+      <c r="M28" s="24"/>
     </row>
     <row r="29" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A29" s="34"/>
-      <c r="B29" s="29"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
-      <c r="M29" s="20"/>
+      <c r="A29" s="37"/>
+      <c r="B29" s="33"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="24"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="24"/>
+      <c r="K29" s="24"/>
+      <c r="L29" s="24"/>
+      <c r="M29" s="24"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A30" s="34"/>
-      <c r="B30" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="C30" s="24"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-      <c r="K30" s="20"/>
-      <c r="L30" s="20"/>
-      <c r="M30" s="20"/>
+      <c r="A30" s="37"/>
+      <c r="B30" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="24"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="24"/>
+      <c r="K30" s="24"/>
+      <c r="L30" s="24"/>
+      <c r="M30" s="24"/>
     </row>
     <row r="31" spans="1:13" ht="37.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="34"/>
-      <c r="B31" s="26"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
+      <c r="A31" s="37"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
       <c r="H31" s="16">
         <v>3</v>
       </c>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-      <c r="K31" s="20"/>
-      <c r="L31" s="20"/>
-      <c r="M31" s="20"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="24"/>
+      <c r="K31" s="24"/>
+      <c r="L31" s="24"/>
+      <c r="M31" s="24"/>
     </row>
     <row r="32" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="34"/>
-      <c r="B32" s="26"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-      <c r="K32" s="20"/>
-      <c r="L32" s="20"/>
-      <c r="M32" s="20"/>
+      <c r="A32" s="37"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="24"/>
+      <c r="K32" s="24"/>
+      <c r="L32" s="24"/>
+      <c r="M32" s="24"/>
     </row>
     <row r="33" spans="1:13" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A33" s="34"/>
-      <c r="B33" s="26"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="27"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="I33" s="20"/>
-      <c r="J33" s="20"/>
-      <c r="K33" s="20"/>
-      <c r="L33" s="20"/>
-      <c r="M33" s="20"/>
+      <c r="A33" s="37"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="24"/>
+      <c r="K33" s="24"/>
+      <c r="L33" s="24"/>
+      <c r="M33" s="24"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A34" s="34"/>
-      <c r="B34" s="32" t="s">
-        <v>152</v>
-      </c>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="25"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="20"/>
-      <c r="L34" s="20"/>
-      <c r="M34" s="20"/>
+      <c r="A34" s="37"/>
+      <c r="B34" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="29"/>
+      <c r="I34" s="24"/>
+      <c r="J34" s="24"/>
+      <c r="K34" s="24"/>
+      <c r="L34" s="24"/>
+      <c r="M34" s="24"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A35" s="34"/>
-      <c r="B35" s="26"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="27"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="28"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="20"/>
-      <c r="K35" s="20"/>
-      <c r="L35" s="20"/>
-      <c r="M35" s="20"/>
+      <c r="A35" s="37"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="32"/>
+      <c r="I35" s="24"/>
+      <c r="J35" s="24"/>
+      <c r="K35" s="24"/>
+      <c r="L35" s="24"/>
+      <c r="M35" s="24"/>
     </row>
     <row r="36" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A36" s="35"/>
-      <c r="B36" s="29"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="30"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="31"/>
-      <c r="I36" s="21"/>
-      <c r="J36" s="21"/>
-      <c r="K36" s="21"/>
-      <c r="L36" s="21"/>
-      <c r="M36" s="21"/>
+      <c r="A36" s="38"/>
+      <c r="B36" s="33"/>
+      <c r="C36" s="34"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="34"/>
+      <c r="F36" s="34"/>
+      <c r="G36" s="35"/>
+      <c r="I36" s="25"/>
+      <c r="J36" s="25"/>
+      <c r="K36" s="25"/>
+      <c r="L36" s="25"/>
+      <c r="M36" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="36">

--- a/库存物料清单.xlsx
+++ b/库存物料清单.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PCB_pro\Material\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2ACB08-6741-42F7-B138-463B7FB3C0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EBF380B-6DF0-4DE0-BE12-5FBE753357AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -624,10 +624,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>光耦 PC817插件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2.54mm双排插针贴片/180°；
 2.54mm双排插针(长)/180°；
 2mm双排插针；</t>
@@ -854,6 +850,11 @@
   </si>
   <si>
     <t>MZ62-202/2KΩ/PTC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>光耦 PC817插件
+817贴片</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1221,6 +1222,15 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1234,7 +1244,7 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1260,17 +1270,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1637,28 +1638,28 @@
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>151</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>152</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="33" x14ac:dyDescent="0.45">
@@ -1685,7 +1686,7 @@
         <v>16</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J4" s="5" t="s">
         <v>17</v>
@@ -1700,13 +1701,13 @@
         <v>18</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>19</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>20</v>
@@ -1715,10 +1716,10 @@
         <v>21</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.45">
@@ -1772,10 +1773,10 @@
         <v>25</v>
       </c>
       <c r="H9" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="I9" s="5" t="s">
         <v>159</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>160</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>26</v>
@@ -2077,8 +2078,8 @@
       <c r="I23" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="J23" s="4" t="s">
-        <v>129</v>
+      <c r="J23" s="5" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.45">
@@ -2147,7 +2148,7 @@
         <v>2</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>84</v>
@@ -2252,7 +2253,7 @@
         <v>122</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I32" s="5" t="s">
         <v>123</v>
@@ -2279,16 +2280,16 @@
         <v>128</v>
       </c>
       <c r="G33" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="H33" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="H33" s="5" t="s">
+      <c r="I33" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="I33" s="5" t="s">
+      <c r="J33" s="5" t="s">
         <v>174</v>
-      </c>
-      <c r="J33" s="5" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="53.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -2297,13 +2298,13 @@
         <v>3</v>
       </c>
       <c r="C34" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E34" s="5" t="s">
         <v>176</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>177</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
@@ -2346,508 +2347,528 @@
   <sheetData>
     <row r="1" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A2" s="36">
+      <c r="A2" s="23">
         <v>1</v>
       </c>
-      <c r="B2" s="39" t="s">
-        <v>137</v>
-      </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="27" t="s">
+      <c r="B2" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2" s="32"/>
+      <c r="D2" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="E2" s="32"/>
+      <c r="F2" s="29" t="s">
         <v>134</v>
       </c>
-      <c r="E2" s="29"/>
-      <c r="F2" s="26" t="s">
+      <c r="G2" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="I2" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="J2" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="K2" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="L2" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="M2" s="26" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A3" s="24"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+    </row>
+    <row r="4" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="24"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A5" s="24"/>
+      <c r="B5" s="30" t="s">
         <v>135</v>
       </c>
-      <c r="G2" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="I2" s="23" t="s">
-        <v>148</v>
-      </c>
-      <c r="J2" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="K2" s="26" t="s">
-        <v>133</v>
-      </c>
-      <c r="L2" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="M2" s="23" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A3" s="37"/>
-      <c r="B3" s="30"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
-    </row>
-    <row r="4" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="37"/>
-      <c r="B4" s="33"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="24"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A5" s="37"/>
-      <c r="B5" s="39" t="s">
-        <v>136</v>
-      </c>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="24"/>
-      <c r="M5" s="24"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="27"/>
     </row>
     <row r="6" spans="1:13" ht="27.5" x14ac:dyDescent="0.45">
-      <c r="A6" s="37"/>
-      <c r="B6" s="30"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
+      <c r="A6" s="24"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
       <c r="H6" s="16">
         <v>1</v>
       </c>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="24"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A7" s="37"/>
-      <c r="B7" s="30"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="24"/>
+      <c r="A7" s="24"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="27"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="27"/>
     </row>
     <row r="8" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="37"/>
-      <c r="B8" s="30"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="I8" s="24"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="24"/>
-      <c r="M8" s="24"/>
+      <c r="A8" s="24"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="27"/>
+      <c r="K8" s="27"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="27"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A9" s="37"/>
-      <c r="B9" s="39" t="s">
-        <v>138</v>
-      </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="29"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="24"/>
-      <c r="M9" s="24"/>
+      <c r="A9" s="24"/>
+      <c r="B9" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="32"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="27"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A10" s="37"/>
-      <c r="B10" s="30"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="32"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="24"/>
+      <c r="A10" s="24"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="35"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
     </row>
     <row r="11" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="38"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="35"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
+      <c r="A11" s="25"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="38"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
+      <c r="K11" s="28"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="28"/>
     </row>
     <row r="14" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="15" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A15" s="36">
+      <c r="A15" s="23">
         <v>2</v>
       </c>
-      <c r="B15" s="27" t="s">
-        <v>170</v>
-      </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="G15" s="23" t="s">
+      <c r="B15" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="C15" s="32"/>
+      <c r="D15" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="E15" s="32"/>
+      <c r="F15" s="29" t="s">
+        <v>131</v>
+      </c>
+      <c r="G15" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="I15" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="J15" s="23" t="s">
+      <c r="I15" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="K15" s="23" t="s">
+      <c r="J15" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="K15" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="L15" s="26" t="s">
         <v>143</v>
       </c>
-      <c r="L15" s="23" t="s">
+      <c r="M15" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="M15" s="23" t="s">
-        <v>145</v>
-      </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A16" s="37"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="24"/>
+      <c r="A16" s="24"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="27"/>
     </row>
     <row r="17" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A17" s="37"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="24"/>
-      <c r="M17" s="24"/>
+      <c r="A17" s="24"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="27"/>
+      <c r="K17" s="27"/>
+      <c r="L17" s="27"/>
+      <c r="M17" s="27"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A18" s="37"/>
-      <c r="B18" s="39" t="s">
-        <v>169</v>
-      </c>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="24"/>
-      <c r="M18" s="24"/>
+      <c r="A18" s="24"/>
+      <c r="B18" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="27"/>
+      <c r="K18" s="27"/>
+      <c r="L18" s="27"/>
+      <c r="M18" s="27"/>
     </row>
     <row r="19" spans="1:13" ht="27.5" x14ac:dyDescent="0.45">
-      <c r="A19" s="37"/>
-      <c r="B19" s="30"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
+      <c r="A19" s="24"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
       <c r="H19" s="16">
         <v>2</v>
       </c>
-      <c r="I19" s="24"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="24"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27"/>
+      <c r="K19" s="27"/>
+      <c r="L19" s="27"/>
+      <c r="M19" s="27"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A20" s="37"/>
-      <c r="B20" s="30"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="24"/>
+      <c r="A20" s="24"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="27"/>
+      <c r="K20" s="27"/>
+      <c r="L20" s="27"/>
+      <c r="M20" s="27"/>
     </row>
     <row r="21" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A21" s="37"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="24"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="24"/>
-      <c r="M21" s="24"/>
+      <c r="A21" s="24"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="I21" s="27"/>
+      <c r="J21" s="27"/>
+      <c r="K21" s="27"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="27"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A22" s="37"/>
+      <c r="A22" s="24"/>
       <c r="B22" s="40"/>
       <c r="C22" s="41"/>
       <c r="D22" s="41"/>
       <c r="E22" s="41"/>
       <c r="F22" s="41"/>
       <c r="G22" s="42"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="24"/>
-      <c r="K22" s="24"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="24"/>
+      <c r="I22" s="27"/>
+      <c r="J22" s="27"/>
+      <c r="K22" s="27"/>
+      <c r="L22" s="27"/>
+      <c r="M22" s="27"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A23" s="37"/>
+      <c r="A23" s="24"/>
       <c r="B23" s="43"/>
       <c r="C23" s="44"/>
       <c r="D23" s="44"/>
       <c r="E23" s="44"/>
       <c r="F23" s="44"/>
       <c r="G23" s="45"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="27"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="27"/>
     </row>
     <row r="24" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A24" s="38"/>
+      <c r="A24" s="25"/>
       <c r="B24" s="46"/>
       <c r="C24" s="47"/>
       <c r="D24" s="47"/>
       <c r="E24" s="47"/>
       <c r="F24" s="47"/>
       <c r="G24" s="48"/>
-      <c r="I24" s="25"/>
-      <c r="J24" s="25"/>
-      <c r="K24" s="25"/>
-      <c r="L24" s="25"/>
-      <c r="M24" s="25"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="28"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="28"/>
+      <c r="M24" s="28"/>
     </row>
     <row r="26" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="27" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A27" s="36">
+      <c r="A27" s="23">
         <v>3</v>
       </c>
-      <c r="B27" s="27" t="s">
+      <c r="B27" s="39" t="s">
+        <v>165</v>
+      </c>
+      <c r="C27" s="32"/>
+      <c r="D27" s="39" t="s">
         <v>166</v>
       </c>
-      <c r="C27" s="29"/>
-      <c r="D27" s="27" t="s">
+      <c r="E27" s="32"/>
+      <c r="F27" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="G27" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="I27" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="J27" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="K27" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="L27" s="29" t="s">
+        <v>170</v>
+      </c>
+      <c r="M27" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="E27" s="29"/>
-      <c r="F27" s="26" t="s">
-        <v>131</v>
-      </c>
-      <c r="G27" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="I27" s="23" t="s">
-        <v>142</v>
-      </c>
-      <c r="J27" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="K27" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="L27" s="26" t="s">
-        <v>171</v>
-      </c>
-      <c r="M27" s="26" t="s">
-        <v>168</v>
-      </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A28" s="37"/>
-      <c r="B28" s="30"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="24"/>
-      <c r="I28" s="24"/>
-      <c r="J28" s="24"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="24"/>
-      <c r="M28" s="24"/>
+      <c r="A28" s="24"/>
+      <c r="B28" s="33"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="27"/>
+      <c r="K28" s="27"/>
+      <c r="L28" s="27"/>
+      <c r="M28" s="27"/>
     </row>
     <row r="29" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A29" s="37"/>
-      <c r="B29" s="33"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24"/>
-      <c r="I29" s="24"/>
-      <c r="J29" s="24"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="24"/>
-      <c r="M29" s="24"/>
+      <c r="A29" s="24"/>
+      <c r="B29" s="36"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="36"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
+      <c r="I29" s="27"/>
+      <c r="J29" s="27"/>
+      <c r="K29" s="27"/>
+      <c r="L29" s="27"/>
+      <c r="M29" s="27"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A30" s="37"/>
-      <c r="B30" s="27" t="s">
-        <v>164</v>
-      </c>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="24"/>
-      <c r="G30" s="24"/>
-      <c r="I30" s="24"/>
-      <c r="J30" s="24"/>
-      <c r="K30" s="24"/>
-      <c r="L30" s="24"/>
-      <c r="M30" s="24"/>
+      <c r="A30" s="24"/>
+      <c r="B30" s="39" t="s">
+        <v>163</v>
+      </c>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="I30" s="27"/>
+      <c r="J30" s="27"/>
+      <c r="K30" s="27"/>
+      <c r="L30" s="27"/>
+      <c r="M30" s="27"/>
     </row>
     <row r="31" spans="1:13" ht="37.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="37"/>
-      <c r="B31" s="30"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="24"/>
+      <c r="A31" s="24"/>
+      <c r="B31" s="33"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
       <c r="H31" s="16">
         <v>3</v>
       </c>
-      <c r="I31" s="24"/>
-      <c r="J31" s="24"/>
-      <c r="K31" s="24"/>
-      <c r="L31" s="24"/>
-      <c r="M31" s="24"/>
+      <c r="I31" s="27"/>
+      <c r="J31" s="27"/>
+      <c r="K31" s="27"/>
+      <c r="L31" s="27"/>
+      <c r="M31" s="27"/>
     </row>
     <row r="32" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="37"/>
-      <c r="B32" s="30"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="24"/>
-      <c r="I32" s="24"/>
-      <c r="J32" s="24"/>
-      <c r="K32" s="24"/>
-      <c r="L32" s="24"/>
-      <c r="M32" s="24"/>
+      <c r="A32" s="24"/>
+      <c r="B32" s="33"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
+      <c r="I32" s="27"/>
+      <c r="J32" s="27"/>
+      <c r="K32" s="27"/>
+      <c r="L32" s="27"/>
+      <c r="M32" s="27"/>
     </row>
     <row r="33" spans="1:13" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A33" s="37"/>
-      <c r="B33" s="30"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
-      <c r="I33" s="24"/>
-      <c r="J33" s="24"/>
-      <c r="K33" s="24"/>
-      <c r="L33" s="24"/>
-      <c r="M33" s="24"/>
+      <c r="A33" s="24"/>
+      <c r="B33" s="33"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+      <c r="I33" s="27"/>
+      <c r="J33" s="27"/>
+      <c r="K33" s="27"/>
+      <c r="L33" s="27"/>
+      <c r="M33" s="27"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A34" s="37"/>
-      <c r="B34" s="27" t="s">
-        <v>165</v>
-      </c>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="29"/>
-      <c r="I34" s="24"/>
-      <c r="J34" s="24"/>
-      <c r="K34" s="24"/>
-      <c r="L34" s="24"/>
-      <c r="M34" s="24"/>
+      <c r="A34" s="24"/>
+      <c r="B34" s="39" t="s">
+        <v>164</v>
+      </c>
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="32"/>
+      <c r="I34" s="27"/>
+      <c r="J34" s="27"/>
+      <c r="K34" s="27"/>
+      <c r="L34" s="27"/>
+      <c r="M34" s="27"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A35" s="37"/>
-      <c r="B35" s="30"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="32"/>
-      <c r="I35" s="24"/>
-      <c r="J35" s="24"/>
-      <c r="K35" s="24"/>
-      <c r="L35" s="24"/>
-      <c r="M35" s="24"/>
+      <c r="A35" s="24"/>
+      <c r="B35" s="33"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="35"/>
+      <c r="I35" s="27"/>
+      <c r="J35" s="27"/>
+      <c r="K35" s="27"/>
+      <c r="L35" s="27"/>
+      <c r="M35" s="27"/>
     </row>
     <row r="36" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A36" s="38"/>
-      <c r="B36" s="33"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="35"/>
-      <c r="I36" s="25"/>
-      <c r="J36" s="25"/>
-      <c r="K36" s="25"/>
-      <c r="L36" s="25"/>
-      <c r="M36" s="25"/>
+      <c r="A36" s="25"/>
+      <c r="B36" s="36"/>
+      <c r="C36" s="37"/>
+      <c r="D36" s="37"/>
+      <c r="E36" s="37"/>
+      <c r="F36" s="37"/>
+      <c r="G36" s="38"/>
+      <c r="I36" s="28"/>
+      <c r="J36" s="28"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+      <c r="M36" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="K27:K36"/>
+    <mergeCell ref="L27:L36"/>
+    <mergeCell ref="M27:M36"/>
+    <mergeCell ref="I27:I36"/>
+    <mergeCell ref="B34:G36"/>
+    <mergeCell ref="D27:E29"/>
+    <mergeCell ref="F27:F33"/>
+    <mergeCell ref="G27:G33"/>
+    <mergeCell ref="B30:E33"/>
+    <mergeCell ref="J27:J36"/>
+    <mergeCell ref="I2:I11"/>
+    <mergeCell ref="J2:J11"/>
+    <mergeCell ref="K2:K11"/>
+    <mergeCell ref="L2:L11"/>
+    <mergeCell ref="M2:M11"/>
+    <mergeCell ref="I15:I24"/>
+    <mergeCell ref="J15:J24"/>
+    <mergeCell ref="K15:K24"/>
+    <mergeCell ref="L15:L24"/>
+    <mergeCell ref="M15:M24"/>
     <mergeCell ref="A15:A24"/>
     <mergeCell ref="A27:A36"/>
     <mergeCell ref="A2:A11"/>
@@ -2864,26 +2885,6 @@
     <mergeCell ref="B18:E21"/>
     <mergeCell ref="B22:G24"/>
     <mergeCell ref="B27:C29"/>
-    <mergeCell ref="I15:I24"/>
-    <mergeCell ref="J15:J24"/>
-    <mergeCell ref="K15:K24"/>
-    <mergeCell ref="L15:L24"/>
-    <mergeCell ref="M15:M24"/>
-    <mergeCell ref="I2:I11"/>
-    <mergeCell ref="J2:J11"/>
-    <mergeCell ref="K2:K11"/>
-    <mergeCell ref="L2:L11"/>
-    <mergeCell ref="M2:M11"/>
-    <mergeCell ref="K27:K36"/>
-    <mergeCell ref="L27:L36"/>
-    <mergeCell ref="M27:M36"/>
-    <mergeCell ref="I27:I36"/>
-    <mergeCell ref="B34:G36"/>
-    <mergeCell ref="D27:E29"/>
-    <mergeCell ref="F27:F33"/>
-    <mergeCell ref="G27:G33"/>
-    <mergeCell ref="B30:E33"/>
-    <mergeCell ref="J27:J36"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
